--- a/grupos/1AM - Estadisticos 20211.xlsx
+++ b/grupos/1AM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -185,24 +185,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,18 +215,54 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>EVANGELISTA</t>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>CUAQUEHUA</t>
   </si>
   <si>
     <t>ESPINOSA</t>
   </si>
   <si>
+    <t>FERNANDEZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -236,15 +272,12 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>LOYO</t>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>LORENZO</t>
   </si>
   <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
     <t>MAYO</t>
   </si>
   <si>
@@ -257,6 +290,12 @@
     <t>MOLOHUA</t>
   </si>
   <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -269,40 +308,55 @@
     <t>SANDOVAL</t>
   </si>
   <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
     <t>TERRAZAS</t>
   </si>
   <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
     <t>VIVAS</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>DIMAS</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>ROSETE</t>
   </si>
   <si>
-    <t>NERI</t>
-  </si>
-  <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>SOLIS</t>
@@ -314,39 +368,54 @@
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>AMECA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
+    <t>SAMUEL</t>
+  </si>
+  <si>
     <t>CRISTIAN ALEXIS</t>
   </si>
   <si>
     <t>CRISTHIAN</t>
   </si>
   <si>
-    <t>JUAN GERARDO</t>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>CARLOS DANIEL</t>
   </si>
   <si>
     <t>ALEXANDER</t>
   </si>
   <si>
+    <t>EVELIN MAYRIN</t>
+  </si>
+  <si>
     <t>MARIO</t>
   </si>
   <si>
+    <t>FELIX RAYMUNDO</t>
+  </si>
+  <si>
     <t>SAUL</t>
   </si>
   <si>
     <t>CRISTIAN FERNANDO</t>
   </si>
   <si>
-    <t>DIEGO ARMANDO</t>
+    <t>MIGUEL</t>
   </si>
   <si>
     <t>ROBERTO</t>
   </si>
   <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
     <t>LUIS OMAR</t>
   </si>
   <si>
@@ -356,9 +425,21 @@
     <t>CHARBEL</t>
   </si>
   <si>
+    <t>TAURINO</t>
+  </si>
+  <si>
     <t>YAHIR</t>
   </si>
   <si>
+    <t>GONZALO</t>
+  </si>
+  <si>
+    <t>CHRISTIAN GABRIEL</t>
+  </si>
+  <si>
+    <t>EYTHAN</t>
+  </si>
+  <si>
     <t>JHOSUA LEVY</t>
   </si>
   <si>
@@ -371,97 +452,16 @@
     <t>JONATHAN</t>
   </si>
   <si>
+    <t>MANUEL</t>
+  </si>
+  <si>
     <t>MARIA REYNA</t>
   </si>
   <si>
+    <t>ADALY</t>
+  </si>
+  <si>
     <t>CHRISTOFER</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>DIMAS</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SAMUEL</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>CARLOS DANIEL</t>
-  </si>
-  <si>
-    <t>EVELIN MAYRIN</t>
-  </si>
-  <si>
-    <t>FELIX RAYMUNDO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>TAURINO</t>
-  </si>
-  <si>
-    <t>GONZALO</t>
-  </si>
-  <si>
-    <t>CHRISTIAN GABRIEL</t>
-  </si>
-  <si>
-    <t>EYTHAN</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>ADALY</t>
   </si>
 </sst>
 </file>
@@ -947,7 +947,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>7</v>
@@ -965,19 +965,19 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1001,19 +1001,19 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>9</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -1042,19 +1042,19 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1087,7 +1087,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1101,19 +1101,19 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1125,7 +1125,7 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1155,19 +1155,19 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1196,19 +1196,19 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1232,7 +1232,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>9</v>
@@ -1244,7 +1244,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1273,19 +1273,19 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1309,13 +1309,13 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>9</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1332,7 +1332,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>9</v>
@@ -1356,13 +1356,13 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1386,7 +1386,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1395,7 +1395,7 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -1409,19 +1409,19 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>6</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1433,13 +1433,13 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1463,19 +1463,19 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1504,19 +1504,19 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1546,13 +1546,13 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1563,37 +1563,37 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C12">
         <v>8</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>6</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1617,19 +1617,19 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>6</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1658,19 +1658,19 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1703,7 +1703,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1717,7 +1717,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>9</v>
@@ -1738,16 +1738,16 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1771,13 +1771,13 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1800,7 +1800,7 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>6</v>
@@ -1812,19 +1812,19 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1851,16 +1851,16 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1889,19 +1889,19 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1937,7 +1937,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -1948,7 +1948,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -1957,7 +1957,7 @@
         <v>7</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -1969,16 +1969,16 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2002,19 +2002,19 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>6</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -2025,19 +2025,19 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>6</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>-1</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -2046,16 +2046,16 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2079,19 +2079,19 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>6</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>-1</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2102,19 +2102,19 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>-1</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>-1</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2126,7 +2126,7 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2156,19 +2156,19 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>-1</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2179,7 +2179,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -2191,7 +2191,7 @@
         <v>9</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -2200,13 +2200,13 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2233,19 +2233,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
         <v>7</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2256,7 +2256,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C21">
         <v>9</v>
@@ -2268,25 +2268,25 @@
         <v>9</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2310,10 +2310,10 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2322,7 +2322,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2339,7 +2339,7 @@
         <v>8</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E22">
         <v>9</v>
@@ -2351,19 +2351,19 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2387,16 +2387,16 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2431,16 +2431,16 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2467,13 +2467,13 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2487,7 +2487,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C24">
         <v>9</v>
@@ -2505,19 +2505,19 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2541,16 +2541,16 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>8</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>8</v>
@@ -2582,19 +2582,19 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2662,16 +2662,16 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2698,13 +2698,13 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>7</v>
@@ -2718,19 +2718,19 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C27">
         <v>6</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>9</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -2742,13 +2742,13 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2772,19 +2772,19 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>6</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>9</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -2813,19 +2813,19 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2855,13 +2855,13 @@
         <v>9</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>9</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2872,16 +2872,16 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D29">
         <v>6</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
         <v>6</v>
@@ -2893,13 +2893,13 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2926,16 +2926,16 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -2949,7 +2949,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>6</v>
@@ -2970,16 +2970,16 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3003,13 +3003,13 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3026,7 +3026,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C31">
         <v>7</v>
@@ -3044,19 +3044,19 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3080,16 +3080,16 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>8</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3121,19 +3121,19 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3160,10 +3160,10 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3180,16 +3180,16 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C33">
         <v>7</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <v>6</v>
@@ -3201,16 +3201,16 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3234,16 +3234,16 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>7</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>6</v>
@@ -3275,16 +3275,16 @@
         <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3311,16 +3311,16 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>8</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>6</v>
@@ -3334,7 +3334,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C35">
         <v>9</v>
@@ -3352,19 +3352,19 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3388,19 +3388,19 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U35">
         <v>9</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3411,19 +3411,19 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>6</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -3432,16 +3432,16 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3465,19 +3465,19 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>6</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3506,19 +3506,19 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3548,13 +3548,13 @@
         <v>9</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W37">
         <v>10</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>10</v>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3622,30 +3622,30 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>70.59</v>
+      </c>
+      <c r="G2">
+        <v>29.41</v>
+      </c>
+      <c r="H2">
+        <v>7.6</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>44.12</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>9.5</v>
-      </c>
-      <c r="I2">
-        <v>19</v>
-      </c>
-      <c r="J2">
-        <v>55.88</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3654,30 +3654,30 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>79.41</v>
+      </c>
+      <c r="G3">
+        <v>20.59</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>70.59</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>7.8</v>
-      </c>
-      <c r="I3">
-        <v>10</v>
-      </c>
-      <c r="J3">
-        <v>29.41</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3686,19 +3686,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>70.59</v>
+        <v>79.41</v>
       </c>
       <c r="G4">
-        <v>29.41</v>
+        <v>20.59</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3709,7 +3709,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3718,30 +3718,30 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>73.53</v>
+        <v>94.12</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>26.47</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3750,30 +3750,30 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>82.34999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>17.65</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -3782,25 +3782,25 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>97.06</v>
+      </c>
+      <c r="G7">
+        <v>2.94</v>
+      </c>
+      <c r="H7">
+        <v>7.2</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>85.29000000000001</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>7.9</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>14.71</v>
       </c>
     </row>
   </sheetData>
@@ -3810,7 +3810,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3839,982 +3839,82 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920152</v>
+        <v>21330051920156</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920152</v>
+        <v>21330051920164</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920152</v>
+        <v>21330051920166</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920152</v>
+        <v>21330051920166</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920152</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920153</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920156</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920156</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920156</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920156</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920157</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920159</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920159</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920159</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920161</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920162</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920164</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920164</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920164</v>
-      </c>
-      <c r="B20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920164</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920165</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920165</v>
-      </c>
-      <c r="B23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" t="s">
-        <v>107</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920166</v>
-      </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920166</v>
-      </c>
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920166</v>
-      </c>
-      <c r="B26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D26" t="s">
-        <v>108</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920166</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920166</v>
-      </c>
-      <c r="B28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920167</v>
-      </c>
-      <c r="B29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920167</v>
-      </c>
-      <c r="B30" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" t="s">
-        <v>109</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920168</v>
-      </c>
-      <c r="B31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920168</v>
-      </c>
-      <c r="B32" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920169</v>
-      </c>
-      <c r="B33" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" t="s">
-        <v>71</v>
-      </c>
-      <c r="D33" t="s">
-        <v>111</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920171</v>
-      </c>
-      <c r="B34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" t="s">
-        <v>112</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920175</v>
-      </c>
-      <c r="B35" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" t="s">
-        <v>95</v>
-      </c>
-      <c r="D35" t="s">
-        <v>113</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920175</v>
-      </c>
-      <c r="B36" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920175</v>
-      </c>
-      <c r="B37" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920176</v>
-      </c>
-      <c r="B38" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" t="s">
-        <v>96</v>
-      </c>
-      <c r="D38" t="s">
-        <v>114</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920176</v>
-      </c>
-      <c r="B39" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" t="s">
-        <v>114</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920176</v>
-      </c>
-      <c r="B40" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D40" t="s">
-        <v>114</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920177</v>
-      </c>
-      <c r="B41" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" t="s">
-        <v>66</v>
-      </c>
-      <c r="D41" t="s">
-        <v>115</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920178</v>
-      </c>
-      <c r="B42" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" t="s">
-        <v>97</v>
-      </c>
-      <c r="D42" t="s">
-        <v>116</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920180</v>
-      </c>
-      <c r="B43" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" t="s">
-        <v>69</v>
-      </c>
-      <c r="D43" t="s">
-        <v>117</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920180</v>
-      </c>
-      <c r="B44" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" t="s">
-        <v>69</v>
-      </c>
-      <c r="D44" t="s">
-        <v>117</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920180</v>
-      </c>
-      <c r="B45" t="s">
-        <v>83</v>
-      </c>
-      <c r="C45" t="s">
-        <v>69</v>
-      </c>
-      <c r="D45" t="s">
-        <v>117</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920182</v>
-      </c>
-      <c r="B46" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" t="s">
-        <v>77</v>
-      </c>
-      <c r="D46" t="s">
-        <v>118</v>
-      </c>
-      <c r="E46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920183</v>
-      </c>
-      <c r="B47" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" t="s">
-        <v>98</v>
-      </c>
-      <c r="D47" t="s">
-        <v>108</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920183</v>
-      </c>
-      <c r="B48" t="s">
-        <v>84</v>
-      </c>
-      <c r="C48" t="s">
-        <v>98</v>
-      </c>
-      <c r="D48" t="s">
-        <v>108</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920183</v>
-      </c>
-      <c r="B49" t="s">
-        <v>84</v>
-      </c>
-      <c r="C49" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" t="s">
-        <v>108</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920183</v>
-      </c>
-      <c r="B50" t="s">
-        <v>84</v>
-      </c>
-      <c r="C50" t="s">
-        <v>98</v>
-      </c>
-      <c r="D50" t="s">
-        <v>108</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4850,373 +3950,373 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920152</v>
+        <v>21330051920166</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920166</v>
+        <v>21330051920156</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920156</v>
+        <v>21330051920164</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920164</v>
+        <v>21330051920151</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920183</v>
+        <v>21330051920152</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920159</v>
+        <v>21330051920153</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920175</v>
+        <v>21330051920154</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920176</v>
+        <v>21330051920155</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920180</v>
+        <v>21330051920157</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920165</v>
+        <v>21330051920158</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920167</v>
+        <v>21330051920159</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920168</v>
+        <v>21330051920160</v>
       </c>
       <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" t="s">
         <v>76</v>
       </c>
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920153</v>
+        <v>21330051920161</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920157</v>
+        <v>21330051920162</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920161</v>
+        <v>21330051920163</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920162</v>
+        <v>21330051920165</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920169</v>
+        <v>21330051920167</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920171</v>
+        <v>21330051920168</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920177</v>
+        <v>21330051920169</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920178</v>
+        <v>21330051920170</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920182</v>
+        <v>21330051920171</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920151</v>
+        <v>21330051920172</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5224,16 +4324,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920154</v>
+        <v>21330051920173</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5241,16 +4341,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920155</v>
+        <v>21330051920174</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5258,16 +4358,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920158</v>
+        <v>21330051920175</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5275,16 +4375,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920160</v>
+        <v>21330051920176</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5292,16 +4392,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920163</v>
+        <v>21330051920177</v>
       </c>
       <c r="B28" t="s">
         <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5309,16 +4409,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920170</v>
+        <v>21330051920178</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5326,16 +4426,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920172</v>
+        <v>21330051920179</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5343,16 +4443,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920173</v>
+        <v>21330051920180</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5360,16 +4460,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920174</v>
+        <v>21330051920181</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5377,16 +4477,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920179</v>
+        <v>21330051920182</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5394,16 +4494,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920181</v>
+        <v>21330051920183</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5414,13 +4514,13 @@
         <v>21330051920184</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5433,7 +4533,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5465,42 +4565,42 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920162</v>
+        <v>21330051920152</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920162</v>
+        <v>21330051920159</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>57</v>
@@ -5511,232 +4611,163 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920168</v>
+        <v>21330051920162</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920168</v>
+        <v>21330051920165</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920153</v>
+        <v>21330051920173</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920157</v>
+        <v>21330051920175</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>55</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920161</v>
+        <v>21330051920176</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920169</v>
+        <v>21330051920177</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920171</v>
+        <v>21330051920180</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>55</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920177</v>
-      </c>
-      <c r="B11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920178</v>
-      </c>
-      <c r="B12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920182</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1AM - Estadisticos 20211.xlsx
+++ b/grupos/1AM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -185,13 +185,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
     <t>García Sánchez Magda Bexabe</t>
@@ -980,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1057,7 +1057,7 @@
         <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1134,7 +1134,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1170,7 +1170,7 @@
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1211,7 +1211,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1247,7 +1247,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1288,7 +1288,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1365,7 +1365,7 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1401,7 +1401,7 @@
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1442,7 +1442,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1519,7 +1519,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1596,7 +1596,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1632,7 +1632,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1673,7 +1673,7 @@
         <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1750,7 +1750,7 @@
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1786,7 +1786,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1827,7 +1827,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1904,7 +1904,7 @@
         <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1940,7 +1940,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1981,7 +1981,7 @@
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2017,7 +2017,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2058,7 +2058,7 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2135,7 +2135,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2212,7 +2212,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2289,7 +2289,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2366,7 +2366,7 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2402,7 +2402,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2443,7 +2443,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2520,7 +2520,7 @@
         <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2597,7 +2597,7 @@
         <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2633,7 +2633,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2674,7 +2674,7 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2751,7 +2751,7 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2828,7 +2828,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2864,7 +2864,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2905,7 +2905,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2941,7 +2941,7 @@
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2982,7 +2982,7 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3059,7 +3059,7 @@
         <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3095,7 +3095,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3136,7 +3136,7 @@
         <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3172,7 +3172,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3213,7 +3213,7 @@
         <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3249,7 +3249,7 @@
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3290,7 +3290,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3367,7 +3367,7 @@
         <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3444,7 +3444,7 @@
         <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3480,7 +3480,7 @@
         <v>6</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3521,7 +3521,7 @@
         <v>9</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3622,19 +3622,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>70.59</v>
+        <v>79.41</v>
       </c>
       <c r="G2">
-        <v>29.41</v>
+        <v>20.59</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3666,7 +3666,7 @@
         <v>20.59</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3686,19 +3686,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>79.41</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="G4">
-        <v>20.59</v>
+        <v>17.65</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4533,7 +4533,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4565,19 +4565,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920152</v>
+        <v>21330051920183</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>55</v>
@@ -4588,22 +4588,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920159</v>
+        <v>21330051920183</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4611,22 +4611,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920162</v>
+        <v>21330051920159</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4634,22 +4634,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920165</v>
+        <v>21330051920162</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4672,7 +4672,7 @@
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4695,7 +4695,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4718,7 +4718,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4741,32 +4741,9 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920180</v>
-      </c>
-      <c r="B10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" t="s">
-        <v>145</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20211.xlsx
+++ b/grupos/1AM - Estadisticos 20211.xlsx
@@ -2132,7 +2132,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -2902,7 +2902,7 @@
         <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>9</v>
@@ -3287,7 +3287,7 @@
         <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>8</v>

--- a/grupos/1AM - Estadisticos 20211.xlsx
+++ b/grupos/1AM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="148">
   <si>
     <t>Materia</t>
   </si>
@@ -185,21 +185,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
+    <t>Ortega Valle Manuel</t>
   </si>
   <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
@@ -215,205 +215,205 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>CUAQUEHUA</t>
+  </si>
+  <si>
     <t>EVANGELISTA</t>
   </si>
   <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>FERNANDEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>LOYO</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
     <t>MACARIO</t>
   </si>
   <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>TERRAZAS</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>VIVAS</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>DIMAS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
   </si>
   <si>
     <t>NERI</t>
   </si>
   <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>AMECA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>SAMUEL</t>
+  </si>
+  <si>
+    <t>CRISTIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>CARLOS DANIEL</t>
+  </si>
+  <si>
     <t>JUAN GERARDO</t>
   </si>
   <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>EVELIN MAYRIN</t>
+  </si>
+  <si>
+    <t>MARIO</t>
+  </si>
+  <si>
+    <t>FELIX RAYMUNDO</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
     <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>TERRAZAS</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>VIVAS</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DIMAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>SAMUEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>CARLOS DANIEL</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>EVELIN MAYRIN</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
-    <t>FELIX RAYMUNDO</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
   </si>
   <si>
     <t>LUIS OMAR</t>
@@ -983,31 +983,31 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>8</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1060,40 +1060,40 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>8</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1119,40 +1119,40 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1161,7 +1161,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1214,37 +1214,37 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>9</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1291,37 +1291,37 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>9</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1350,10 +1350,10 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>8</v>
@@ -1368,31 +1368,31 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>8</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1401,7 +1401,7 @@
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1412,7 +1412,7 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1427,10 +1427,10 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1445,37 +1445,37 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>6</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1522,22 +1522,22 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1546,13 +1546,13 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1599,31 +1599,31 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>7</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1676,22 +1676,22 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1706,7 +1706,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1735,7 +1735,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -1753,25 +1753,25 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1780,13 +1780,13 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1830,40 +1830,40 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1907,37 +1907,37 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>6</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1966,7 +1966,7 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>6</v>
@@ -1984,22 +1984,22 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -2011,7 +2011,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2034,7 +2034,7 @@
         <v>5</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F18">
         <v>6</v>
@@ -2043,7 +2043,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -2052,7 +2052,7 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>6</v>
@@ -2061,22 +2061,22 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -2085,13 +2085,13 @@
         <v>6</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2105,13 +2105,13 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F19">
         <v>6</v>
@@ -2120,16 +2120,16 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -2138,34 +2138,34 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -2197,7 +2197,7 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>6</v>
@@ -2209,40 +2209,40 @@
         <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>5</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>5</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2283,7 +2283,7 @@
         <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>6</v>
@@ -2292,34 +2292,34 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>9</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2369,25 +2369,25 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2396,7 +2396,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2428,7 +2428,7 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -2446,40 +2446,40 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>7</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2523,40 +2523,40 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>8</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2600,25 +2600,25 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>8</v>
@@ -2627,7 +2627,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>9</v>
@@ -2659,7 +2659,7 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
         <v>7</v>
@@ -2677,40 +2677,40 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2736,10 +2736,10 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -2754,34 +2754,34 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>6</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -2831,22 +2831,22 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2855,7 +2855,7 @@
         <v>9</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2890,7 +2890,7 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -2908,28 +2908,28 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -2938,10 +2938,10 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2967,7 +2967,7 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>9</v>
@@ -2985,25 +2985,25 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -3015,10 +3015,10 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3062,37 +3062,37 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>8</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3139,34 +3139,34 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
         <v>10</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -3198,7 +3198,7 @@
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
         <v>6</v>
@@ -3216,28 +3216,28 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V33">
         <v>6</v>
@@ -3249,7 +3249,7 @@
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3293,40 +3293,40 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3370,40 +3370,40 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>8</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3429,7 +3429,7 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I36">
         <v>7</v>
@@ -3438,7 +3438,7 @@
         <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>6</v>
@@ -3447,31 +3447,31 @@
         <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>6</v>
@@ -3524,22 +3524,22 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3548,7 +3548,7 @@
         <v>9</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3622,19 +3622,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>79.41</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="G2">
-        <v>20.59</v>
+        <v>14.71</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3654,19 +3654,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>79.41</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G3">
-        <v>20.59</v>
+        <v>8.82</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3686,19 +3686,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>82.34999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="G4">
-        <v>17.65</v>
+        <v>2.94</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3709,7 +3709,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3718,30 +3718,30 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3750,25 +3750,25 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3782,19 +3782,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3810,7 +3810,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3835,86 +3835,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920156</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920164</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920166</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920166</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3950,64 +3870,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920166</v>
+        <v>21330051920151</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920156</v>
+        <v>21330051920152</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920164</v>
+        <v>21330051920153</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920151</v>
+        <v>21330051920154</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
         <v>119</v>
@@ -4018,13 +3938,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920152</v>
+        <v>21330051920155</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
         <v>120</v>
@@ -4035,13 +3955,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920153</v>
+        <v>21330051920156</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
         <v>121</v>
@@ -4052,13 +3972,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920154</v>
+        <v>21330051920157</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
         <v>122</v>
@@ -4069,13 +3989,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920155</v>
+        <v>21330051920158</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
         <v>123</v>
@@ -4086,13 +4006,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920157</v>
+        <v>21330051920159</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
         <v>124</v>
@@ -4103,13 +4023,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920158</v>
+        <v>21330051920160</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
         <v>125</v>
@@ -4120,13 +4040,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920159</v>
+        <v>21330051920161</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
         <v>126</v>
@@ -4137,13 +4057,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920160</v>
+        <v>21330051920162</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
         <v>127</v>
@@ -4154,13 +4074,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920161</v>
+        <v>21330051920163</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
         <v>128</v>
@@ -4171,13 +4091,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920162</v>
+        <v>21330051920164</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
         <v>129</v>
@@ -4188,13 +4108,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920163</v>
+        <v>21330051920165</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
         <v>130</v>
@@ -4205,13 +4125,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920165</v>
+        <v>21330051920166</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
         <v>131</v>
@@ -4225,10 +4145,10 @@
         <v>21330051920167</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
         <v>132</v>
@@ -4242,10 +4162,10 @@
         <v>21330051920168</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4259,10 +4179,10 @@
         <v>21330051920169</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
@@ -4276,10 +4196,10 @@
         <v>21330051920170</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
@@ -4293,10 +4213,10 @@
         <v>21330051920171</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4310,10 +4230,10 @@
         <v>21330051920172</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -4327,10 +4247,10 @@
         <v>21330051920173</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -4344,10 +4264,10 @@
         <v>21330051920174</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -4361,10 +4281,10 @@
         <v>21330051920175</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4378,10 +4298,10 @@
         <v>21330051920176</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4395,10 +4315,10 @@
         <v>21330051920177</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4412,10 +4332,10 @@
         <v>21330051920178</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -4429,10 +4349,10 @@
         <v>21330051920179</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
         <v>144</v>
@@ -4446,10 +4366,10 @@
         <v>21330051920180</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
         <v>145</v>
@@ -4463,10 +4383,10 @@
         <v>21330051920181</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
         <v>146</v>
@@ -4480,10 +4400,10 @@
         <v>21330051920182</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s">
         <v>147</v>
@@ -4497,13 +4417,13 @@
         <v>21330051920183</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -4514,13 +4434,13 @@
         <v>21330051920184</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -4533,7 +4453,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4565,22 +4485,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920183</v>
+        <v>21330051920156</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4588,22 +4508,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920183</v>
+        <v>21330051920156</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4611,19 +4531,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920159</v>
+        <v>21330051920164</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>56</v>
@@ -4634,13 +4554,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920162</v>
+        <v>21330051920164</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
         <v>129</v>
@@ -4649,7 +4569,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4657,22 +4577,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920173</v>
+        <v>21330051920166</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4680,22 +4600,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920175</v>
+        <v>21330051920166</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4703,47 +4623,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920176</v>
+        <v>21330051920175</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920177</v>
-      </c>
-      <c r="B9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20211.xlsx
+++ b/grupos/1AM - Estadisticos 20211.xlsx
@@ -2452,7 +2452,7 @@
         <v>7</v>
       </c>
       <c r="P23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>6</v>
